--- a/TKH_SYSTEM/frontend/templates/student-import-template.xlsx
+++ b/TKH_SYSTEM/frontend/templates/student-import-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phat.ngo\Desktop\TKH PROJECT\TKH_SYSTEM\frontend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1773A35-D17E-408F-95E1-56B14CE89446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB45F03A-C863-4334-AA70-317122D7217A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B114F50D-8FFF-43C7-8BA5-DFD0ACB85915}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
   <si>
     <t>Giới tính</t>
   </si>
@@ -65,14 +65,71 @@
     <t>Ti-mô-thê</t>
   </si>
   <si>
-    <t>Họ và Tên</t>
+    <t>Nguyễn Văn 3</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 4</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 5</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 6</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 7</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 8</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 9</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 10</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 11</t>
+  </si>
+  <si>
+    <t>Nữ</t>
+  </si>
+  <si>
+    <t>Họ và tên</t>
+  </si>
+  <si>
+    <t>Trịnh Thiên Phú</t>
+  </si>
+  <si>
+    <t>Nê-hê-mi</t>
+  </si>
+  <si>
+    <t>Phạm Bá Nam</t>
+  </si>
+  <si>
+    <t>Ma-ry</t>
+  </si>
+  <si>
+    <t>Ca-lép</t>
+  </si>
+  <si>
+    <t>Sa-ra</t>
+  </si>
+  <si>
+    <t>Giô-na-than</t>
+  </si>
+  <si>
+    <t>Giê-rê-mi</t>
+  </si>
+  <si>
+    <t>Ê-xơ-ra</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +141,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -448,10 +511,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6E91B3-A24A-4522-89E5-76E2987A12D6}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
     <col min="3" max="3" width="12.88671875" customWidth="1"/>
     <col min="4" max="4" width="15.44140625" customWidth="1"/>
     <col min="5" max="5" width="16.109375" customWidth="1"/>
@@ -459,7 +522,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -476,7 +539,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -488,10 +551,198 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="D2" numberStoredAsText="1"/>

--- a/TKH_SYSTEM/frontend/templates/student-import-template.xlsx
+++ b/TKH_SYSTEM/frontend/templates/student-import-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phat.ngo\Desktop\TKH PROJECT\TKH_SYSTEM\frontend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB45F03A-C863-4334-AA70-317122D7217A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C04D8F-1B67-4326-9E01-66D699E91E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B114F50D-8FFF-43C7-8BA5-DFD0ACB85915}"/>
   </bookViews>
@@ -107,9 +107,6 @@
     <t>Phạm Bá Nam</t>
   </si>
   <si>
-    <t>Ma-ry</t>
-  </si>
-  <si>
     <t>Ca-lép</t>
   </si>
   <si>
@@ -123,6 +120,9 @@
   </si>
   <si>
     <t>Ê-xơ-ra</t>
+  </si>
+  <si>
+    <t>Ma-ri</t>
   </si>
 </sst>
 </file>
@@ -585,7 +585,7 @@
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -602,7 +602,7 @@
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -619,7 +619,7 @@
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -636,7 +636,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -653,7 +653,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -670,7 +670,7 @@
         <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">

--- a/TKH_SYSTEM/frontend/templates/student-import-template.xlsx
+++ b/TKH_SYSTEM/frontend/templates/student-import-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phat.ngo\Desktop\TKH PROJECT\TKH_SYSTEM\frontend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C04D8F-1B67-4326-9E01-66D699E91E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89C3C42-AE38-4BCE-8774-CD17728F9ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B114F50D-8FFF-43C7-8BA5-DFD0ACB85915}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="67">
   <si>
     <t>Giới tính</t>
   </si>
@@ -123,6 +123,123 @@
   </si>
   <si>
     <t>Ma-ri</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 12</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 13</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 14</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 15</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 16</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 17</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 18</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 19</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 20</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 21</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 22</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 23</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 24</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 25</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 26</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 27</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 28</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 29</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 30</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 31</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 32</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 33</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 34</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 35</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 36</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 37</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 38</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 39</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 40</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 41</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 42</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 43</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 44</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 45</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 46</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 47</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 48</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 49</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn 50</t>
   </si>
 </sst>
 </file>
@@ -511,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6E91B3-A24A-4522-89E5-76E2987A12D6}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" customWidth="1"/>
@@ -576,7 +693,7 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1">
         <v>35777</v>
@@ -739,6 +856,669 @@
       </c>
       <c r="E13" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>65</v>
+      </c>
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="1">
+        <v>35777</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
